--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2019_nuble.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2019_nuble.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:31</t>
+    <t xml:space="preserve">2026-09-09 20:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2019_nuble.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2019_nuble.xlsx
@@ -24,69 +24,69 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Chillán</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bulnes</t>
   </si>
   <si>
-    <t xml:space="preserve">Chillán</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chillán Viejo</t>
   </si>
   <si>
+    <t xml:space="preserve">El Carmen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pemuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Ignacio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yungay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quirihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cobquecura</t>
   </si>
   <si>
     <t xml:space="preserve">Coelemu</t>
   </si>
   <si>
+    <t xml:space="preserve">Ninhue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portezuelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ránquil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treguaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Carlos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coihueco</t>
   </si>
   <si>
-    <t xml:space="preserve">El Carmen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ninhue</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ñiquén</t>
   </si>
   <si>
-    <t xml:space="preserve">Pemuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pinto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portezuelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quillón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quirihue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ránquil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Carlos</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Fabián</t>
   </si>
   <si>
-    <t xml:space="preserve">San Ignacio</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Nicolás</t>
   </si>
   <si>
-    <t xml:space="preserve">Treguaco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yungay</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:32</t>
+    <t xml:space="preserve">2026-09-18 10:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>73.7</v>
+        <v>76.29</v>
       </c>
     </row>
     <row r="3">
@@ -516,7 +516,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>76.29</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="4">
@@ -532,7 +532,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>76.89</v>
+        <v>73.52</v>
       </c>
     </row>
     <row r="6">
@@ -540,7 +540,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>76.52</v>
+        <v>72.94</v>
       </c>
     </row>
     <row r="7">
@@ -548,7 +548,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>72.12</v>
+        <v>72.67</v>
       </c>
     </row>
     <row r="8">
@@ -556,7 +556,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>73.52</v>
+        <v>73.77</v>
       </c>
     </row>
     <row r="9">
@@ -564,7 +564,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>74.19</v>
+        <v>71.89</v>
       </c>
     </row>
     <row r="10">
@@ -572,7 +572,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>72.51</v>
+        <v>77.61</v>
       </c>
     </row>
     <row r="11">
@@ -580,7 +580,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>72.94</v>
+        <v>77.07</v>
       </c>
     </row>
     <row r="12">
@@ -588,7 +588,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>72.67</v>
+        <v>76.89</v>
       </c>
     </row>
     <row r="13">
@@ -596,7 +596,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>76.42</v>
+        <v>76.52</v>
       </c>
     </row>
     <row r="14">
@@ -604,7 +604,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>73.77</v>
+        <v>74.19</v>
       </c>
     </row>
     <row r="15">
@@ -612,7 +612,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>77.07</v>
+        <v>76.42</v>
       </c>
     </row>
     <row r="16">
@@ -628,7 +628,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>74.97</v>
+        <v>72.81</v>
       </c>
     </row>
     <row r="18">
@@ -636,7 +636,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>73.76</v>
+        <v>74.97</v>
       </c>
     </row>
     <row r="19">
@@ -644,7 +644,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>71.89</v>
+        <v>72.12</v>
       </c>
     </row>
     <row r="20">
@@ -652,7 +652,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>72.63</v>
+        <v>72.51</v>
       </c>
     </row>
     <row r="21">
@@ -660,7 +660,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>72.81</v>
+        <v>73.76</v>
       </c>
     </row>
     <row r="22">
@@ -668,7 +668,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>77.61</v>
+        <v>72.63</v>
       </c>
     </row>
   </sheetData>
